--- a/data/Тест по теме Конкурентные отношения (Биоинженеры) (Ответы).xlsx
+++ b/data/Тест по теме Конкурентные отношения (Биоинженеры) (Ответы).xlsx
@@ -1,17 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <bookViews>
+    <workbookView windowWidth="22188" windowHeight="9324"/>
+  </bookViews>
   <sheets>
-    <sheet state="visible" name="Ответы на форму (1)" sheetId="1" r:id="rId5"/>
+    <sheet name="Ответы на форму (1)" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="60">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="62">
   <si>
     <t>Отметка времени</t>
   </si>
@@ -191,112 +207,1072 @@
   </si>
   <si>
     <t>С большим количеством трофических уровней в сообществе, С парадоксом планктона</t>
+  </si>
+  <si>
+    <t>st150414</t>
+  </si>
+  <si>
+    <t>st097958</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="m/d/yyyy h:mm:ss"/>
-    <numFmt numFmtId="165" formatCode="0&quot; / 10&quot;"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="7">
+    <numFmt numFmtId="176" formatCode="_-* #\.##0.00_-;\-* #\.##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-* #\.##0.00\ &quot;₽&quot;_-;\-* #\.##0.00\ &quot;₽&quot;_-;_-* \-??\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-* #\.##0_-;\-* #\.##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+    <numFmt numFmtId="179" formatCode="_-* #\.##0\ &quot;₽&quot;_-;\-* #\.##0\ &quot;₽&quot;_-;_-* \-\ &quot;₽&quot;_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="m/d/yyyy\ h:mm:ss"/>
+    <numFmt numFmtId="181" formatCode="0&quot; / 10&quot;"/>
+    <numFmt numFmtId="182" formatCode="dd\.mm\.yyyy\ h:mm"/>
   </numFmts>
-  <fonts count="3">
-    <font>
-      <sz val="10.0"/>
+  <fonts count="24">
+    <font>
+      <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <i/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Roboto"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Arial"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="lightGray"/>
+      <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF8F9FA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
-  <borders count="1">
-    <border/>
+  <borders count="16">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFF8F9FA"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF442F65"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFFFFFFF"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFF8F9FA"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFF8F9FA"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF442F65"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF442F65"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
+  <cellStyleXfs count="49">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="8" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="12" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="11" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="13" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="14" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="15" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="164" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="165" xfId="0" applyAlignment="1" applyFont="1" applyNumberFormat="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf quotePrefix="1" borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+  <cellXfs count="13">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="181" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="182" fontId="3" fillId="3" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" quotePrefix="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle xfId="0" name="Normal" builtinId="0"/>
+  <cellStyles count="49">
+    <cellStyle name="Обычный" xfId="0" builtinId="0"/>
+    <cellStyle name="Запятая" xfId="1" builtinId="3"/>
+    <cellStyle name="Денежный" xfId="2" builtinId="4"/>
+    <cellStyle name="Процент" xfId="3" builtinId="5"/>
+    <cellStyle name="Запятая [0]" xfId="4" builtinId="6"/>
+    <cellStyle name="Денежный [0]" xfId="5" builtinId="7"/>
+    <cellStyle name="Гиперссылка" xfId="6" builtinId="8"/>
+    <cellStyle name="Открывавшаяся гиперссылка" xfId="7" builtinId="9"/>
+    <cellStyle name="Примечание" xfId="8" builtinId="10"/>
+    <cellStyle name="Предупреждающий текст" xfId="9" builtinId="11"/>
+    <cellStyle name="Заголовок" xfId="10" builtinId="15"/>
+    <cellStyle name="Пояснительный текст" xfId="11" builtinId="53"/>
+    <cellStyle name="Заголовок 1" xfId="12" builtinId="16"/>
+    <cellStyle name="Заголовок 2" xfId="13" builtinId="17"/>
+    <cellStyle name="Заголовок 3" xfId="14" builtinId="18"/>
+    <cellStyle name="Заголовок 4" xfId="15" builtinId="19"/>
+    <cellStyle name="Ввод" xfId="16" builtinId="20"/>
+    <cellStyle name="Вывод" xfId="17" builtinId="21"/>
+    <cellStyle name="Вычисление" xfId="18" builtinId="22"/>
+    <cellStyle name="Проверить ячейку" xfId="19" builtinId="23"/>
+    <cellStyle name="Связанная ячейка" xfId="20" builtinId="24"/>
+    <cellStyle name="Итого" xfId="21" builtinId="25"/>
+    <cellStyle name="Хороший" xfId="22" builtinId="26"/>
+    <cellStyle name="Плохой" xfId="23" builtinId="27"/>
+    <cellStyle name="Нейтральный" xfId="24" builtinId="28"/>
+    <cellStyle name="Акцент1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% — Акцент1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% — Акцент1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% — Акцент1" xfId="28" builtinId="32"/>
+    <cellStyle name="Акцент2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% — Акцент2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% — Акцент2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% — Акцент2" xfId="32" builtinId="36"/>
+    <cellStyle name="Акцент3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% — Акцент3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% — Акцент3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% — Акцент3" xfId="36" builtinId="40"/>
+    <cellStyle name="Акцент4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% — Акцент4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% — Акцент4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% — Акцент4" xfId="40" builtinId="44"/>
+    <cellStyle name="Акцент5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% — Акцент5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% — Акцент5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% — Акцент5" xfId="44" builtinId="48"/>
+    <cellStyle name="Акцент6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% — Акцент6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% — Акцент6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% — Акцент6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="17">
     <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="none"/>
-      </fill>
-      <border/>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
     </dxf>
     <dxf>
-      <font/>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="Arial"/>
+        <scheme val="minor"/>
+        <charset val="134"/>
+        <family val="0"/>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <u val="none"/>
+        <sz val="10"/>
+        <color rgb="FF000000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8F9FA"/>
+          <bgColor rgb="FFF8F9FA"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF5B3F86"/>
           <bgColor rgb="FF5B3F86"/>
         </patternFill>
       </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFFFFFFF"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <border/>
-    </dxf>
-    <dxf>
-      <font/>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8F9FA"/>
-          <bgColor rgb="FFF8F9FA"/>
-        </patternFill>
-      </fill>
-      <border/>
     </dxf>
     <dxf>
       <border>
@@ -316,47 +1292,44 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="4" pivot="0" name="Ответы на форму (1)-style">
-      <tableStyleElement dxfId="1" type="headerRow"/>
-      <tableStyleElement dxfId="2" type="firstRowStripe"/>
-      <tableStyleElement dxfId="3" type="secondRowStripe"/>
-      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    <tableStyle name="Ответы на форму (1)-style" pivot="0" count="4" xr9:uid="{43FECEBA-BAAB-44CA-BCF4-E0532E907E06}">
+      <tableStyleElement type="wholeTable" dxfId="16"/>
+      <tableStyleElement type="headerRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="secondRowStripe" dxfId="13"/>
     </tableStyle>
   </tableStyles>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<x18tc:personList xmlns:x18tc="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments"/>
-</file>
-
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:M12" displayName="Form_Responses" name="Form_Responses" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Form_Responses" displayName="Form_Responses" ref="A1:M12">
   <tableColumns count="13">
-    <tableColumn name="Отметка времени" id="1"/>
-    <tableColumn name="Баллы" id="2"/>
-    <tableColumn name="Найдите себя в списке" id="3"/>
-    <tableColumn name="В каком из примеров говорится о конкурентных отношениях, проявляющихся в интерференции?" id="4"/>
-    <tableColumn name="Знаменитый эколог-теоретик Роберт Мак-Артур высказал мнение, что термин «экологическая ниша» очень близок к другому биологическому понятию. Какому?" id="5"/>
-    <tableColumn name="Перед вами рисунок, демонстрирующий соотношение экологических ниш двух видов и экологической лицензии некоторого биотопа. Какими номерами обозначены диапазоны значений ресурса, которые точно входят в реализованные ниши вида А и вида В." id="6"/>
-    <tableColumn name="Перед вами рисунок, демонстрирующий соотношение экологических ниш двух видов и экологической лицензии некоторого биотопа. Что можно сказать про про диапазон ресурсов, обозначенный номером 2." id="7"/>
-    <tableColumn name="Перед вами рисунок, демонстрирующий соотношение экологических ниш двух видов и экологической лицензии некоторого биотопа. Какими номерами обозначена фундаментальная ниша вида А." id="8"/>
-    <tableColumn name="Перед вами рисунок, демонстрирующий соотношение экологических ниш двух видов и экологической лицензии некоторого биотопа. Какими номерами обозначены диапазоны ресурсов, за которые потенциально может идти конкуренция между видом А и видом В" id="9"/>
-    <tableColumn name="Перед вами рисунок, демонстрирующий соотношение экологических ниш двух видов и экологической лицензии некоторого биотопа. Какими номерами обозначены диапазоны ресурсов, которые, вероятно, отсутствуют в данном биотопе." id="10"/>
-    <tableColumn name="Пусть есть два конкурирующих вида. У вида 1 мальтузианский параметр составляет r = 0.6, а емкость среды для него K= 600 особей. У второго вида мальтузианский параметр составляет r = 0.2, а емкость среды - K = 200 особей. При этом известно, что степень отрицательного влияния со стороны первого вида составляет 0.1. При какой степени отрицательного влияния со стороны вида 2 будет происходить конкурентное исключение вида 1." id="11"/>
-    <tableColumn name="В каких случаях может не происходить конкурентное исключение одного из двух видов, сосуществующих в одном биотопе?" id="12"/>
-    <tableColumn name="Если в среде, в которой представлено некоторое сообщество, количество ресурсов очень ограничено, однако это сообщество сформировано большим количеством видов, то с чем мы сталкиваемся в данном случае?" id="13"/>
+    <tableColumn id="1" name="Отметка времени" dataDxfId="0"/>
+    <tableColumn id="2" name="Баллы" dataDxfId="1"/>
+    <tableColumn id="3" name="Найдите себя в списке" dataDxfId="2"/>
+    <tableColumn id="4" name="В каком из примеров говорится о конкурентных отношениях, проявляющихся в интерференции?" dataDxfId="3"/>
+    <tableColumn id="5" name="Знаменитый эколог-теоретик Роберт Мак-Артур высказал мнение, что термин «экологическая ниша» очень близок к другому биологическому понятию. Какому?" dataDxfId="4"/>
+    <tableColumn id="6" name="Перед вами рисунок, демонстрирующий соотношение экологических ниш двух видов и экологической лицензии некоторого биотопа. Какими номерами обозначены диапазоны значений ресурса, которые точно входят в реализованные ниши вида А и вида В." dataDxfId="5"/>
+    <tableColumn id="7" name="Перед вами рисунок, демонстрирующий соотношение экологических ниш двух видов и экологической лицензии некоторого биотопа. Что можно сказать про про диапазон ресурсов, обозначенный номером 2." dataDxfId="6"/>
+    <tableColumn id="8" name="Перед вами рисунок, демонстрирующий соотношение экологических ниш двух видов и экологической лицензии некоторого биотопа. Какими номерами обозначена фундаментальная ниша вида А." dataDxfId="7"/>
+    <tableColumn id="9" name="Перед вами рисунок, демонстрирующий соотношение экологических ниш двух видов и экологической лицензии некоторого биотопа. Какими номерами обозначены диапазоны ресурсов, за которые потенциально может идти конкуренция между видом А и видом В" dataDxfId="8"/>
+    <tableColumn id="10" name="Перед вами рисунок, демонстрирующий соотношение экологических ниш двух видов и экологической лицензии некоторого биотопа. Какими номерами обозначены диапазоны ресурсов, которые, вероятно, отсутствуют в данном биотопе." dataDxfId="9"/>
+    <tableColumn id="11" name="Пусть есть два конкурирующих вида. У вида 1 мальтузианский параметр составляет r = 0.6, а емкость среды для него K= 600 особей. У второго вида мальтузианский параметр составляет r = 0.2, а емкость среды - K = 200 особей. При этом известно, что степень отрицательного влияния со стороны первого вида составляет 0.1. При какой степени отрицательного влияния со стороны вида 2 будет происходить конкурентное исключение вида 1." dataDxfId="10"/>
+    <tableColumn id="12" name="В каких случаях может не происходить конкурентное исключение одного из двух видов, сосуществующих в одном биотопе?" dataDxfId="11"/>
+    <tableColumn id="13" name="Если в среде, в которой представлено некоторое сообщество, количество ресурсов очень ограничено, однако это сообщество сформировано большим количеством видов, то с чем мы сталкиваемся в данном случае?" dataDxfId="12"/>
   </tableColumns>
-  <tableStyleInfo name="Ответы на форму (1)-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Ответы на форму (1)-style" showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheets">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
     <a:clrScheme name="Sheets">
       <a:dk1>
@@ -546,24 +1519,26 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <dimension ref="A1:S14"/>
+  <sheetFormatPr defaultColWidth="12.6296296296296" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="19.0"/>
-    <col customWidth="1" min="2" max="2" width="18.88"/>
-    <col customWidth="1" min="3" max="3" width="22.88"/>
-    <col customWidth="1" min="4" max="13" width="37.63"/>
-    <col customWidth="1" min="14" max="19" width="18.88"/>
+    <col min="1" max="1" width="19" customWidth="1"/>
+    <col min="2" max="2" width="18.8796296296296" customWidth="1"/>
+    <col min="3" max="3" width="22.8796296296296" customWidth="1"/>
+    <col min="4" max="13" width="37.6296296296296" customWidth="1"/>
+    <col min="14" max="19" width="18.8796296296296" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="22.5" customHeight="1">
+    <row r="1" ht="22.5" customHeight="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -604,12 +1579,12 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" ht="22.5" customHeight="1">
+    <row r="2" ht="22.5" customHeight="1" spans="1:13">
       <c r="A2" s="3">
-        <v>46086.53237339121</v>
+        <v>46086.5323733912</v>
       </c>
       <c r="B2" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>13</v>
@@ -620,7 +1595,7 @@
       <c r="E2" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="13" t="s">
         <v>16</v>
       </c>
       <c r="G2" s="5" t="s">
@@ -645,12 +1620,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="3" ht="22.5" customHeight="1">
+    <row r="3" ht="22.5" customHeight="1" spans="1:13">
       <c r="A3" s="3">
         <v>46087.8377115162</v>
       </c>
       <c r="B3" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>24</v>
@@ -674,7 +1649,7 @@
         <v>19</v>
       </c>
       <c r="J3" s="5">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>29</v>
@@ -686,12 +1661,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="4" ht="22.5" customHeight="1">
+    <row r="4" ht="22.5" customHeight="1" spans="1:13">
       <c r="A4" s="3">
-        <v>46087.90154523148</v>
+        <v>46087.9015452315</v>
       </c>
       <c r="B4" s="4">
-        <v>5.0</v>
+        <v>5</v>
       </c>
       <c r="C4" s="5" t="s">
         <v>31</v>
@@ -702,7 +1677,7 @@
       <c r="E4" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="13" t="s">
         <v>33</v>
       </c>
       <c r="G4" s="5" t="s">
@@ -727,12 +1702,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="5" ht="22.5" customHeight="1">
+    <row r="5" ht="22.5" customHeight="1" spans="1:13">
       <c r="A5" s="3">
-        <v>46087.922914675924</v>
+        <v>46087.9229146759</v>
       </c>
       <c r="B5" s="4">
-        <v>9.0</v>
+        <v>9</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>36</v>
@@ -768,12 +1743,12 @@
         <v>39</v>
       </c>
     </row>
-    <row r="6" ht="22.5" customHeight="1">
+    <row r="6" ht="22.5" customHeight="1" spans="1:13">
       <c r="A6" s="3">
-        <v>46087.92575922454</v>
+        <v>46087.9257592245</v>
       </c>
       <c r="B6" s="4">
-        <v>8.0</v>
+        <v>8</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>40</v>
@@ -785,7 +1760,7 @@
         <v>26</v>
       </c>
       <c r="F6" s="5">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="G6" s="5" t="s">
         <v>17</v>
@@ -796,7 +1771,7 @@
       <c r="I6" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="13" t="s">
         <v>41</v>
       </c>
       <c r="K6" s="5" t="s">
@@ -809,12 +1784,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" ht="22.5" customHeight="1">
+    <row r="7" ht="22.5" customHeight="1" spans="1:13">
       <c r="A7" s="3">
-        <v>46087.95115849537</v>
+        <v>46087.9511584954</v>
       </c>
       <c r="B7" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>42</v>
@@ -850,12 +1825,12 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" ht="22.5" customHeight="1">
+    <row r="8" ht="22.5" customHeight="1" spans="1:13">
       <c r="A8" s="3">
-        <v>46087.953620949076</v>
+        <v>46087.9536209491</v>
       </c>
       <c r="B8" s="4">
-        <v>10.0</v>
+        <v>10</v>
       </c>
       <c r="C8" s="5" t="s">
         <v>45</v>
@@ -891,12 +1866,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" ht="22.5" customHeight="1">
+    <row r="9" ht="22.5" customHeight="1" spans="1:13">
       <c r="A9" s="3">
-        <v>46087.97575424769</v>
+        <v>46087.9757542477</v>
       </c>
       <c r="B9" s="4">
-        <v>4.0</v>
+        <v>4</v>
       </c>
       <c r="C9" s="5" t="s">
         <v>46</v>
@@ -907,7 +1882,7 @@
       <c r="E9" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="13" t="s">
         <v>33</v>
       </c>
       <c r="G9" s="5" t="s">
@@ -932,12 +1907,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="10" ht="22.5" customHeight="1">
+    <row r="10" ht="22.5" customHeight="1" spans="1:13">
       <c r="A10" s="3">
         <v>46087.9766174074</v>
       </c>
       <c r="B10" s="4">
-        <v>3.0</v>
+        <v>3</v>
       </c>
       <c r="C10" s="5" t="s">
         <v>51</v>
@@ -948,7 +1923,7 @@
       <c r="E10" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="13" t="s">
         <v>33</v>
       </c>
       <c r="G10" s="5" t="s">
@@ -973,12 +1948,12 @@
         <v>23</v>
       </c>
     </row>
-    <row r="11" ht="22.5" customHeight="1">
+    <row r="11" ht="22.5" customHeight="1" spans="1:13">
       <c r="A11" s="3">
-        <v>46087.982846388884</v>
+        <v>46087.9828463889</v>
       </c>
       <c r="B11" s="4">
-        <v>1.0</v>
+        <v>1</v>
       </c>
       <c r="C11" s="5" t="s">
         <v>53</v>
@@ -1014,12 +1989,12 @@
         <v>57</v>
       </c>
     </row>
-    <row r="12" ht="22.5" customHeight="1">
+    <row r="12" ht="22.5" customHeight="1" spans="1:13">
       <c r="A12" s="3">
         <v>46087.9843046875</v>
       </c>
       <c r="B12" s="4">
-        <v>6.0</v>
+        <v>6</v>
       </c>
       <c r="C12" s="5" t="s">
         <v>58</v>
@@ -1055,10 +2030,105 @@
         <v>59</v>
       </c>
     </row>
+    <row r="13" customHeight="1" spans="1:19">
+      <c r="A13" s="6">
+        <v>46094.1112962963</v>
+      </c>
+      <c r="B13" s="4">
+        <v>10</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>25</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="H13" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>19</v>
+      </c>
+      <c r="J13" s="7" t="s">
+        <v>20</v>
+      </c>
+      <c r="K13" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="N13" s="11"/>
+      <c r="O13" s="11"/>
+      <c r="P13" s="11"/>
+      <c r="Q13" s="11"/>
+      <c r="R13" s="11"/>
+      <c r="S13" s="11"/>
+    </row>
+    <row r="14" customHeight="1" spans="1:19">
+      <c r="A14" s="8">
+        <v>46094.9936689815</v>
+      </c>
+      <c r="B14" s="4">
+        <v>10</v>
+      </c>
+      <c r="C14" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="E14" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="F14" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="H14" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="I14" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="J14" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="K14" s="9" t="s">
+        <v>38</v>
+      </c>
+      <c r="L14" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="N14" s="11"/>
+      <c r="O14" s="11"/>
+      <c r="P14" s="11"/>
+      <c r="Q14" s="11"/>
+      <c r="R14" s="11"/>
+      <c r="S14" s="11"/>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
   <tableParts count="1">
-    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId1"/>
   </tableParts>
 </worksheet>
 </file>